--- a/Result/profitability/1464.xlsx
+++ b/Result/profitability/1464.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.3</v>
       </c>
       <c r="M2" t="n">
-        <v>0.12375</v>
+        <v>0.09875000000000002</v>
       </c>
       <c r="N2" t="n">
-        <v>18.0925</v>
+        <v>17.67875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.08125000000000002</v>
+        <v>0.04250000000000002</v>
       </c>
       <c r="N3" t="n">
-        <v>17.20375</v>
+        <v>17.58875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02500000000000002</v>
+        <v>-0.03124999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>16.69</v>
+        <v>16.2525</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.37</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.08624999999999999</v>
+        <v>-0.02374999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>15.2725</v>
+        <v>15.07625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.04</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.01124999999999999</v>
+        <v>-0.02124999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>14.94875</v>
+        <v>15.22375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.17</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.007499999999999986</v>
+        <v>-0.03999999999999998</v>
       </c>
       <c r="N7" t="n">
-        <v>15.18125</v>
+        <v>15.03875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.04749999999999999</v>
+        <v>-0.07749999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>14.91</v>
+        <v>14.58125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1774,7 +1774,7 @@
         <v>0.2</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.02124999999999998</v>
+        <v>-0.02124999999999999</v>
       </c>
       <c r="N11" t="n">
         <v>15.12375</v>
@@ -1901,7 +1901,7 @@
         <v>0.03</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.008749999999999983</v>
+        <v>-0.008749999999999987</v>
       </c>
       <c r="N12" t="n">
         <v>15.73</v>
@@ -9360,23 +9360,23 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>4.04%</t>
+          <t>4.03%</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>-442</v>
+        <v>-351</v>
       </c>
       <c r="J71" t="n">
-        <v>-328</v>
+        <v>-238</v>
       </c>
       <c r="K71" t="n">
-        <v>-260</v>
+        <v>-173</v>
       </c>
       <c r="L71" t="n">
-        <v>-0.64</v>
+        <v>-0.43</v>
       </c>
       <c r="M71" t="n">
-        <v>0.12625</v>
+        <v>0.1525</v>
       </c>
       <c r="N71" t="n">
         <v>18.81125</v>
@@ -9406,10 +9406,10 @@
         <v>114.2</v>
       </c>
       <c r="W71" t="n">
-        <v>-1.16</v>
+        <v>-0.95</v>
       </c>
       <c r="X71" t="n">
-        <v>-2.230769230769231</v>
+        <v>-1.826923076923077</v>
       </c>
       <c r="Y71" t="n">
         <v>-1.93</v>
@@ -9418,10 +9418,10 @@
         <v>-0.08873563218390801</v>
       </c>
       <c r="AA71" t="n">
-        <v>-0.89</v>
+        <v>-0.6799999999999999</v>
       </c>
       <c r="AB71" t="n">
-        <v>-3.56</v>
+        <v>-2.72</v>
       </c>
       <c r="AC71" t="n">
         <v>-1.780000000000001</v>
@@ -9491,25 +9491,25 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>64</v>
+        <v>-27</v>
       </c>
       <c r="J72" t="n">
-        <v>50</v>
+        <v>-41</v>
       </c>
       <c r="K72" t="n">
-        <v>61</v>
+        <v>-27</v>
       </c>
       <c r="L72" t="n">
-        <v>0.14</v>
+        <v>-0.06</v>
       </c>
       <c r="M72" t="n">
-        <v>0.13375</v>
+        <v>0.135</v>
       </c>
       <c r="N72" t="n">
         <v>19.08</v>
       </c>
       <c r="O72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P72" t="n">
         <v>0</v>
@@ -9533,10 +9533,10 @@
         <v>114.3</v>
       </c>
       <c r="W72" t="n">
-        <v>0.78</v>
+        <v>0.37</v>
       </c>
       <c r="X72" t="n">
-        <v>-1.21875</v>
+        <v>-0.8604651162790697</v>
       </c>
       <c r="Y72" t="n">
         <v>-3.77</v>
@@ -9545,10 +9545,10 @@
         <v>-0.1902119071644803</v>
       </c>
       <c r="AA72" t="n">
-        <v>-0.13</v>
+        <v>-0.33</v>
       </c>
       <c r="AB72" t="n">
-        <v>-0.4814814814814815</v>
+        <v>-1.222222222222222</v>
       </c>
       <c r="AC72" t="n">
         <v>-5.509999999999998</v>
@@ -9630,7 +9630,7 @@
         <v>0.32</v>
       </c>
       <c r="M73" t="n">
-        <v>0.17125</v>
+        <v>0.1725</v>
       </c>
       <c r="N73" t="n">
         <v>19.11375</v>
@@ -9660,10 +9660,10 @@
         <v>114.4</v>
       </c>
       <c r="W73" t="n">
-        <v>0.18</v>
+        <v>0.38</v>
       </c>
       <c r="X73" t="n">
-        <v>1.285714285714286</v>
+        <v>-6.333333333333334</v>
       </c>
       <c r="Y73" t="n">
         <v>3.34</v>
@@ -9757,7 +9757,7 @@
         <v>0.3</v>
       </c>
       <c r="M74" t="n">
-        <v>0.1925</v>
+        <v>0.19375</v>
       </c>
       <c r="N74" t="n">
         <v>19.5275</v>
@@ -9838,6 +9838,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1464</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2959</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2419</v>
+      </c>
+      <c r="E75" t="n">
+        <v>540</v>
+      </c>
+      <c r="F75" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="G75" t="n">
+        <v>73</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.46%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-35</v>
+      </c>
+      <c r="J75" t="n">
+        <v>38</v>
+      </c>
+      <c r="K75" t="n">
+        <v>25</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="N75" t="n">
+        <v>19.10875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.629999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1259578544061303</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.13953488372093</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.07921291624621596</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
